--- a/Data/raw/Purchasing behavior.xlsx
+++ b/Data/raw/Purchasing behavior.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b6a8a74c1ce5fdf/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\project-waste\Data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5091AB97-449E-49D5-8554-DCC23FD9EB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0444FE15-6E6E-466C-8670-AB3BD09B55E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CBB85223-4E72-4DC4-A04D-D1C20855DD31}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>hotel food frders per month</t>
   </si>
@@ -59,12 +59,16 @@
   <si>
     <t>list_frequency</t>
   </si>
+  <si>
+    <t xml:space="preserve">Ward No.
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +89,27 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Roboto"/>
     </font>
@@ -142,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -166,6 +191,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -181,10 +220,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,10 +519,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{414101ED-2868-4423-99CB-5E6A7D197BAD}">
-  <dimension ref="A1:H513"/>
+  <dimension ref="A1:I514"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="8.90625" style="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="91" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="91" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -512,8 +550,11 @@
       <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -538,8 +579,11 @@
       <c r="H2" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I2" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -564,8 +608,11 @@
       <c r="H3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I3" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -590,8 +637,11 @@
       <c r="H4" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I4" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -616,8 +666,11 @@
       <c r="H5" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I5" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -642,8 +695,11 @@
       <c r="H6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I6" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -668,8 +724,11 @@
       <c r="H7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I7" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -694,8 +753,11 @@
       <c r="H8" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I8" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -718,8 +780,11 @@
       <c r="H9" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -744,8 +809,11 @@
       <c r="H10" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I10" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -770,8 +838,11 @@
       <c r="H11" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -794,8 +865,11 @@
       <c r="H12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -820,8 +894,11 @@
       <c r="H13" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -846,8 +923,11 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I14" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -872,8 +952,11 @@
       <c r="H15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I15" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -896,8 +979,11 @@
       <c r="H16" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I16" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -920,8 +1006,11 @@
       <c r="H17" s="5">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I17" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -944,8 +1033,11 @@
       <c r="H18" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -968,8 +1060,11 @@
       <c r="H19" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I19" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -992,8 +1087,11 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I20" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1018,8 +1116,11 @@
       <c r="H21" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I21" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1044,8 +1145,11 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I22" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1068,8 +1172,11 @@
       <c r="H23" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I23" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1092,8 +1199,11 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I24" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1116,8 +1226,11 @@
       <c r="H25" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I25" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1140,8 +1253,11 @@
       <c r="H26" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I26" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1166,8 +1282,11 @@
       <c r="H27" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I27" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1192,8 +1311,11 @@
       <c r="H28" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I28" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1214,8 +1336,11 @@
       <c r="H29" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I29" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1238,8 +1363,11 @@
       <c r="H30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I30" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1262,8 +1390,11 @@
       <c r="H31" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I31" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1286,8 +1417,11 @@
       <c r="H32" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I32" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1308,8 +1442,11 @@
       <c r="H33" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I33" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1332,8 +1469,11 @@
       <c r="H34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I34" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1358,8 +1498,11 @@
       <c r="H35" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I35" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1384,8 +1527,11 @@
       <c r="H36" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I36" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1410,8 +1556,11 @@
       <c r="H37" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I37" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1430,8 +1579,11 @@
       <c r="H38" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I38" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1456,8 +1608,11 @@
       <c r="H39" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I39" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1480,8 +1635,11 @@
       <c r="H40" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I40" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1506,8 +1664,11 @@
       <c r="H41" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I41" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1532,8 +1693,11 @@
       <c r="H42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I42" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1558,8 +1722,11 @@
       <c r="H43" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I43" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1584,8 +1751,11 @@
       <c r="H44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I44" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1610,8 +1780,11 @@
       <c r="H45" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I45" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1636,8 +1809,11 @@
       <c r="H46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I46" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1660,8 +1836,11 @@
       <c r="H47" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I47" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1686,8 +1865,11 @@
       <c r="H48" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I48" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1710,8 +1892,11 @@
       <c r="H49" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I49" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1734,8 +1919,11 @@
       <c r="H50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I50" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1758,8 +1946,11 @@
       <c r="H51" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I51" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1784,8 +1975,11 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I52" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1810,8 +2004,11 @@
       <c r="H53" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I53" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1836,8 +2033,11 @@
       <c r="H54" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I54" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1862,8 +2062,11 @@
       <c r="H55" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I55" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1888,8 +2091,11 @@
       <c r="H56" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I56" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1914,8 +2120,11 @@
       <c r="H57" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I57" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1940,8 +2149,11 @@
       <c r="H58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I58" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1964,8 +2176,11 @@
       <c r="H59" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I59" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1990,8 +2205,11 @@
       <c r="H60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I60" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2016,8 +2234,11 @@
       <c r="H61" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I61" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2042,8 +2263,11 @@
       <c r="H62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I62" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2066,8 +2290,11 @@
       <c r="H63" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I63" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2090,8 +2317,11 @@
       <c r="H64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I64" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2116,8 +2346,11 @@
       <c r="H65" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I65" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -2142,8 +2375,11 @@
       <c r="H66" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I66" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -2168,8 +2404,11 @@
       <c r="H67" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I67" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -2192,8 +2431,11 @@
       <c r="H68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I68" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2216,8 +2458,11 @@
       <c r="H69" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I69" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -2242,8 +2487,11 @@
       <c r="H70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I70" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -2268,8 +2516,11 @@
       <c r="H71" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I71" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -2294,8 +2545,11 @@
       <c r="H72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I72" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -2316,8 +2570,11 @@
       <c r="H73" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I73" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -2342,8 +2599,11 @@
       <c r="H74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I74" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -2366,8 +2626,11 @@
       <c r="H75" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I75" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -2390,8 +2653,11 @@
       <c r="H76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I76" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -2414,8 +2680,11 @@
       <c r="H77" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I77" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -2438,8 +2707,11 @@
       <c r="H78" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I78" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -2462,8 +2734,11 @@
       <c r="H79" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I79" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -2486,8 +2761,11 @@
       <c r="H80" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I80" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -2512,8 +2790,11 @@
       <c r="H81" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I81" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -2538,8 +2819,11 @@
       <c r="H82" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I82" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -2562,8 +2846,11 @@
       <c r="H83" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I83" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -2588,8 +2875,11 @@
       <c r="H84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I84" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -2614,8 +2904,11 @@
       <c r="H85" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I85" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -2640,8 +2933,11 @@
       <c r="H86" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I86" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -2664,8 +2960,11 @@
       <c r="H87" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I87" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -2688,8 +2987,11 @@
       <c r="H88" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I88" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -2710,8 +3012,11 @@
       <c r="H89" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I89" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -2732,8 +3037,11 @@
       <c r="H90" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I90" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2756,8 +3064,11 @@
       <c r="H91" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I91" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2780,8 +3091,11 @@
       <c r="H92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I92" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2806,8 +3120,11 @@
       <c r="H93" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I93" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2832,8 +3149,11 @@
       <c r="H94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I94" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2858,8 +3178,11 @@
       <c r="H95" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I95" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2884,8 +3207,11 @@
       <c r="H96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I96" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2910,8 +3236,11 @@
       <c r="H97" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I97" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2936,8 +3265,11 @@
       <c r="H98" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I98" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2960,8 +3292,11 @@
       <c r="H99" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I99" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2984,8 +3319,11 @@
       <c r="H100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I100" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -3008,8 +3346,11 @@
       <c r="H101" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I101" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -3034,8 +3375,11 @@
       <c r="H102" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I102" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -3060,8 +3404,11 @@
       <c r="H103" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I103" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -3086,8 +3433,11 @@
       <c r="H104" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I104" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -3112,8 +3462,11 @@
       <c r="H105" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I105" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -3136,8 +3489,11 @@
       <c r="H106" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I106" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -3162,8 +3518,11 @@
       <c r="H107" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I107" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -3188,8 +3547,11 @@
       <c r="H108" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I108" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -3214,8 +3576,11 @@
       <c r="H109" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I109" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -3240,8 +3605,11 @@
       <c r="H110" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I110" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -3266,8 +3634,11 @@
       <c r="H111" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I111" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -3292,8 +3663,11 @@
       <c r="H112" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I112" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -3316,8 +3690,11 @@
       <c r="H113" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I113" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -3340,8 +3717,11 @@
       <c r="H114" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I114" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -3364,8 +3744,11 @@
       <c r="H115" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I115" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -3388,8 +3771,11 @@
       <c r="H116" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I116" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -3412,8 +3798,11 @@
       <c r="H117" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I117" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -3438,8 +3827,11 @@
       <c r="H118" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I118" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -3464,8 +3856,11 @@
       <c r="H119" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I119" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -3488,8 +3883,11 @@
       <c r="H120" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I120" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -3512,8 +3910,11 @@
       <c r="H121" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I121" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -3538,8 +3939,11 @@
       <c r="H122" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I122" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -3564,8 +3968,11 @@
       <c r="H123" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I123" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -3590,8 +3997,11 @@
       <c r="H124" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I124" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -3616,8 +4026,11 @@
       <c r="H125" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I125" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -3640,8 +4053,11 @@
       <c r="H126" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I126" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -3664,8 +4080,11 @@
       <c r="H127" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I127" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -3688,8 +4107,11 @@
       <c r="H128" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I128" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -3712,8 +4134,11 @@
       <c r="H129" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I129" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -3738,8 +4163,11 @@
       <c r="H130" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I130" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -3762,8 +4190,11 @@
       <c r="H131" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I131" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -3788,8 +4219,11 @@
       <c r="H132" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I132" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -3812,8 +4246,11 @@
       <c r="H133" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I133" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -3838,8 +4275,11 @@
       <c r="H134" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I134" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -3862,8 +4302,11 @@
       <c r="H135" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I135" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -3886,8 +4329,11 @@
       <c r="H136" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I136" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -3910,8 +4356,11 @@
       <c r="H137" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I137" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -3936,8 +4385,11 @@
       <c r="H138" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I138" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -3962,8 +4414,11 @@
       <c r="H139" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I139" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -3988,8 +4443,11 @@
       <c r="H140" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I140" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -4014,8 +4472,11 @@
       <c r="H141" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I141" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -4040,8 +4501,11 @@
       <c r="H142" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I142" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -4064,8 +4528,11 @@
       <c r="H143" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I143" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -4090,8 +4557,11 @@
       <c r="H144" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I144" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -4116,8 +4586,11 @@
       <c r="H145" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I145" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -4142,8 +4615,11 @@
       <c r="H146" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I146" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -4168,8 +4644,11 @@
       <c r="H147" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I147" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -4194,8 +4673,11 @@
       <c r="H148" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I148" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -4220,8 +4702,11 @@
       <c r="H149" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I149" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -4246,8 +4731,11 @@
       <c r="H150" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I150" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -4270,8 +4758,11 @@
       <c r="H151" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I151" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -4294,8 +4785,11 @@
       <c r="H152" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I152" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -4318,8 +4812,11 @@
       <c r="H153" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I153" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -4342,8 +4839,11 @@
       <c r="H154" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I154" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -4366,8 +4866,11 @@
       <c r="H155" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I155" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -4390,8 +4893,11 @@
       <c r="H156" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I156" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -4414,8 +4920,11 @@
       <c r="H157" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I157" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -4438,8 +4947,11 @@
       <c r="H158" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I158" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -4464,8 +4976,11 @@
       <c r="H159" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I159" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -4490,8 +5005,11 @@
       <c r="H160" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I160" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -4516,8 +5034,11 @@
       <c r="H161" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I161" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -4540,8 +5061,11 @@
       <c r="H162" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I162" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -4564,8 +5088,11 @@
       <c r="H163" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I163" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -4590,8 +5117,11 @@
       <c r="H164" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I164" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -4616,8 +5146,11 @@
       <c r="H165" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I165" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -4642,8 +5175,11 @@
       <c r="H166" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I166" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -4666,8 +5202,11 @@
       <c r="H167" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I167" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -4692,8 +5231,11 @@
       <c r="H168" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I168" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -4718,8 +5260,11 @@
       <c r="H169" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I169" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -4742,8 +5287,11 @@
       <c r="H170" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I170" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -4766,8 +5314,11 @@
       <c r="H171" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I171" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -4792,8 +5343,11 @@
       <c r="H172" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I172" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -4818,8 +5372,11 @@
       <c r="H173" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I173" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -4844,8 +5401,11 @@
       <c r="H174" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I174" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -4868,8 +5428,11 @@
       <c r="H175" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I175" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -4894,8 +5457,11 @@
       <c r="H176" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I176" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -4920,8 +5486,11 @@
       <c r="H177" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I177" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -4944,8 +5513,11 @@
       <c r="H178" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I178" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -4968,8 +5540,11 @@
       <c r="H179" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I179" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -4992,8 +5567,11 @@
       <c r="H180" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I180" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -5018,8 +5596,11 @@
       <c r="H181" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I181" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -5042,8 +5623,11 @@
       <c r="H182" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I182" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -5066,8 +5650,11 @@
       <c r="H183" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I183" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -5090,8 +5677,11 @@
       <c r="H184" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I184" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -5116,8 +5706,11 @@
       <c r="H185" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I185" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -5142,8 +5735,11 @@
       <c r="H186" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I186" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -5166,8 +5762,11 @@
       <c r="H187" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I187" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -5192,8 +5791,11 @@
       <c r="H188" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I188" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -5216,8 +5818,11 @@
       <c r="H189" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I189" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -5240,8 +5845,11 @@
       <c r="H190" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I190" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -5264,8 +5872,11 @@
       <c r="H191" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I191" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -5288,8 +5899,11 @@
       <c r="H192" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I192" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -5312,8 +5926,11 @@
       <c r="H193" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I193" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -5338,8 +5955,11 @@
       <c r="H194" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I194" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -5362,8 +5982,11 @@
       <c r="H195" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I195" s="12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -5388,8 +6011,11 @@
       <c r="H196" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I196" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -5412,8 +6038,11 @@
       <c r="H197" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I197" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -5436,8 +6065,11 @@
       <c r="H198" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I198" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -5460,8 +6092,11 @@
       <c r="H199" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I199" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -5484,8 +6119,11 @@
       <c r="H200" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I200" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -5510,8 +6148,11 @@
       <c r="H201" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I201" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -5536,8 +6177,11 @@
       <c r="H202" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I202" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -5562,8 +6206,11 @@
       <c r="H203" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I203" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -5588,8 +6235,11 @@
       <c r="H204" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I204" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -5614,8 +6264,11 @@
       <c r="H205" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I205" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -5640,8 +6293,11 @@
       <c r="H206" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I206" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -5664,8 +6320,11 @@
       <c r="H207" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I207" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -5688,8 +6347,11 @@
       <c r="H208" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I208" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -5712,8 +6374,11 @@
       <c r="H209" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I209" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -5738,8 +6403,11 @@
       <c r="H210" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I210" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -5762,8 +6430,11 @@
       <c r="H211" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I211" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -5786,8 +6457,11 @@
       <c r="H212" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I212" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -5810,8 +6484,11 @@
       <c r="H213" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I213" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -5836,8 +6513,11 @@
       <c r="H214" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I214" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -5860,8 +6540,11 @@
       <c r="H215" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I215" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -5886,8 +6569,11 @@
       <c r="H216" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I216" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -5912,8 +6598,11 @@
       <c r="H217" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I217" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -5936,8 +6625,11 @@
       <c r="H218" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I218" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -5960,8 +6652,11 @@
       <c r="H219" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I219" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -5984,8 +6679,11 @@
       <c r="H220" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I220" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -6008,8 +6706,11 @@
       <c r="H221" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I221" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -6032,8 +6733,11 @@
       <c r="H222" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I222" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -6056,8 +6760,11 @@
         <v>0</v>
       </c>
       <c r="H223" s="7"/>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I223" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -6080,8 +6787,11 @@
       <c r="H224" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I224" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -6106,8 +6816,11 @@
       <c r="H225" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I225" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -6130,8 +6843,11 @@
       <c r="H226" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I226" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -6154,8 +6870,11 @@
       <c r="H227" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I227" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -6178,8 +6897,11 @@
       <c r="H228" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I228" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -6202,8 +6924,11 @@
       <c r="H229" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I229" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -6226,8 +6951,11 @@
       <c r="H230" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I230" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -6252,8 +6980,11 @@
       <c r="H231" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I231" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -6276,8 +7007,11 @@
       <c r="H232" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I232" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -6302,8 +7036,11 @@
       <c r="H233" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I233" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -6326,8 +7063,11 @@
       <c r="H234" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I234" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -6352,8 +7092,11 @@
       <c r="H235" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I235" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -6376,8 +7119,11 @@
       <c r="H236" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I236" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -6400,8 +7146,11 @@
       <c r="H237" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I237" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -6426,8 +7175,11 @@
       <c r="H238" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I238" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -6450,8 +7202,11 @@
       <c r="H239" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I239" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -6474,8 +7229,11 @@
       <c r="H240" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I240" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -6498,8 +7256,11 @@
       <c r="H241" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I241" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -6522,8 +7283,11 @@
       <c r="H242" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I242" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -6546,8 +7310,11 @@
       <c r="H243" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I243" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -6570,8 +7337,11 @@
       <c r="H244" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I244" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>244</v>
       </c>
@@ -6594,8 +7364,11 @@
       <c r="H245" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I245" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -6618,8 +7391,11 @@
       <c r="H246" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I246" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -6642,8 +7418,11 @@
       <c r="H247" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I247" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -6668,8 +7447,11 @@
       <c r="H248" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I248" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -6692,8 +7474,11 @@
       <c r="H249" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I249" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -6716,8 +7501,11 @@
       <c r="H250" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I250" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>250</v>
       </c>
@@ -6740,8 +7528,11 @@
       <c r="H251" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I251" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>251</v>
       </c>
@@ -6764,8 +7555,11 @@
       <c r="H252" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I252" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -6790,8 +7584,11 @@
       <c r="H253" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I253" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -6814,8 +7611,11 @@
       <c r="H254" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I254" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>254</v>
       </c>
@@ -6838,8 +7638,11 @@
       <c r="H255" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I255" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>255</v>
       </c>
@@ -6862,8 +7665,11 @@
       <c r="H256" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I256" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>256</v>
       </c>
@@ -6888,8 +7694,11 @@
       <c r="H257" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I257" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>257</v>
       </c>
@@ -6912,8 +7721,11 @@
       <c r="H258" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I258" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>258</v>
       </c>
@@ -6938,8 +7750,11 @@
       <c r="H259" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I259" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>259</v>
       </c>
@@ -6962,8 +7777,11 @@
       <c r="H260" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I260" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>260</v>
       </c>
@@ -6986,8 +7804,11 @@
       <c r="H261" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I261" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>261</v>
       </c>
@@ -7010,8 +7831,11 @@
       <c r="H262" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I262" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>262</v>
       </c>
@@ -7034,8 +7858,11 @@
       <c r="H263" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I263" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>263</v>
       </c>
@@ -7060,8 +7887,11 @@
       <c r="H264" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I264" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>264</v>
       </c>
@@ -7084,8 +7914,11 @@
       <c r="H265" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I265" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>265</v>
       </c>
@@ -7110,8 +7943,11 @@
       <c r="H266" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I266" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>266</v>
       </c>
@@ -7134,8 +7970,11 @@
       <c r="H267" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I267" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -7158,8 +7997,11 @@
       <c r="H268" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I268" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>268</v>
       </c>
@@ -7184,8 +8026,11 @@
       <c r="H269" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I269" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>269</v>
       </c>
@@ -7208,8 +8053,11 @@
       <c r="H270" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I270" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>270</v>
       </c>
@@ -7232,8 +8080,11 @@
       <c r="H271" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I271" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>271</v>
       </c>
@@ -7258,8 +8109,11 @@
       <c r="H272" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I272" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>272</v>
       </c>
@@ -7282,8 +8136,11 @@
       <c r="H273" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I273" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>273</v>
       </c>
@@ -7306,8 +8163,11 @@
       <c r="H274" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I274" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>274</v>
       </c>
@@ -7332,8 +8192,11 @@
       <c r="H275" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I275" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>275</v>
       </c>
@@ -7356,8 +8219,11 @@
       <c r="H276" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I276" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>276</v>
       </c>
@@ -7382,8 +8248,11 @@
       <c r="H277" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I277" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>277</v>
       </c>
@@ -7406,8 +8275,11 @@
       <c r="H278" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I278" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>278</v>
       </c>
@@ -7426,8 +8298,11 @@
       </c>
       <c r="G279" s="7"/>
       <c r="H279" s="7"/>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I279" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>279</v>
       </c>
@@ -7446,8 +8321,11 @@
       </c>
       <c r="G280" s="8"/>
       <c r="H280" s="8"/>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I280" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>280</v>
       </c>
@@ -7466,8 +8344,11 @@
       </c>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I281" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>281</v>
       </c>
@@ -7486,8 +8367,11 @@
       </c>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I282" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>282</v>
       </c>
@@ -7506,8 +8390,11 @@
       </c>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I283" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>283</v>
       </c>
@@ -7526,8 +8413,11 @@
       </c>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I284" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>284</v>
       </c>
@@ -7550,8 +8440,11 @@
       <c r="H285" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I285" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>285</v>
       </c>
@@ -7574,8 +8467,11 @@
       <c r="H286" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I286" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>286</v>
       </c>
@@ -7598,8 +8494,11 @@
       <c r="H287" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I287" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>287</v>
       </c>
@@ -7618,8 +8517,11 @@
       </c>
       <c r="G288" s="8"/>
       <c r="H288" s="8"/>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I288" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>288</v>
       </c>
@@ -7632,8 +8534,11 @@
       <c r="F289" s="7"/>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I289" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>289</v>
       </c>
@@ -7652,8 +8557,11 @@
       </c>
       <c r="G290" s="8"/>
       <c r="H290" s="8"/>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I290" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>290</v>
       </c>
@@ -7672,8 +8580,11 @@
       </c>
       <c r="G291" s="7"/>
       <c r="H291" s="7"/>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I291" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>291</v>
       </c>
@@ -7692,8 +8603,11 @@
       </c>
       <c r="G292" s="8"/>
       <c r="H292" s="8"/>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I292" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>292</v>
       </c>
@@ -7712,8 +8626,11 @@
       </c>
       <c r="G293" s="7"/>
       <c r="H293" s="7"/>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I293" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>293</v>
       </c>
@@ -7732,8 +8649,11 @@
       </c>
       <c r="G294" s="8"/>
       <c r="H294" s="8"/>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I294" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>294</v>
       </c>
@@ -7752,8 +8672,11 @@
       </c>
       <c r="G295" s="7"/>
       <c r="H295" s="7"/>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I295" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>295</v>
       </c>
@@ -7776,8 +8699,11 @@
       <c r="H296" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I296" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>296</v>
       </c>
@@ -7798,8 +8724,11 @@
       </c>
       <c r="G297" s="7"/>
       <c r="H297" s="7"/>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I297" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>297</v>
       </c>
@@ -7818,8 +8747,11 @@
       </c>
       <c r="G298" s="8"/>
       <c r="H298" s="8"/>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I298" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>298</v>
       </c>
@@ -7838,8 +8770,11 @@
       </c>
       <c r="G299" s="7"/>
       <c r="H299" s="7"/>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I299" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>299</v>
       </c>
@@ -7862,8 +8797,11 @@
       <c r="H300" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I300" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>300</v>
       </c>
@@ -7886,8 +8824,11 @@
       <c r="H301" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I301" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>301</v>
       </c>
@@ -7906,8 +8847,11 @@
       </c>
       <c r="G302" s="8"/>
       <c r="H302" s="8"/>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I302" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>302</v>
       </c>
@@ -7928,8 +8872,11 @@
         <v>30</v>
       </c>
       <c r="H303" s="7"/>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I303" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>303</v>
       </c>
@@ -7948,8 +8895,11 @@
       </c>
       <c r="G304" s="8"/>
       <c r="H304" s="8"/>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I304" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>304</v>
       </c>
@@ -7968,8 +8918,11 @@
       </c>
       <c r="G305" s="7"/>
       <c r="H305" s="7"/>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I305" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>305</v>
       </c>
@@ -7988,8 +8941,11 @@
       </c>
       <c r="G306" s="8"/>
       <c r="H306" s="8"/>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I306" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>306</v>
       </c>
@@ -8012,8 +8968,11 @@
       <c r="H307" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I307" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>307</v>
       </c>
@@ -8032,8 +8991,11 @@
       </c>
       <c r="G308" s="8"/>
       <c r="H308" s="8"/>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I308" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>308</v>
       </c>
@@ -8052,8 +9014,11 @@
       </c>
       <c r="G309" s="7"/>
       <c r="H309" s="7"/>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I309" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>309</v>
       </c>
@@ -8072,8 +9037,11 @@
       </c>
       <c r="G310" s="8"/>
       <c r="H310" s="8"/>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I310" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>310</v>
       </c>
@@ -8092,8 +9060,11 @@
       </c>
       <c r="G311" s="7"/>
       <c r="H311" s="7"/>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I311" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>311</v>
       </c>
@@ -8112,8 +9083,11 @@
       </c>
       <c r="G312" s="8"/>
       <c r="H312" s="8"/>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I312" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>312</v>
       </c>
@@ -8132,8 +9106,11 @@
       </c>
       <c r="G313" s="7"/>
       <c r="H313" s="7"/>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I313" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>313</v>
       </c>
@@ -8152,8 +9129,11 @@
       </c>
       <c r="G314" s="8"/>
       <c r="H314" s="8"/>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I314" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>314</v>
       </c>
@@ -8172,8 +9152,11 @@
       </c>
       <c r="G315" s="7"/>
       <c r="H315" s="7"/>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I315" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>315</v>
       </c>
@@ -8192,8 +9175,11 @@
       </c>
       <c r="G316" s="8"/>
       <c r="H316" s="8"/>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I316" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>316</v>
       </c>
@@ -8212,8 +9198,11 @@
       </c>
       <c r="G317" s="7"/>
       <c r="H317" s="7"/>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I317" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>317</v>
       </c>
@@ -8232,8 +9221,11 @@
       </c>
       <c r="G318" s="8"/>
       <c r="H318" s="8"/>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I318" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>318</v>
       </c>
@@ -8252,8 +9244,11 @@
       </c>
       <c r="G319" s="7"/>
       <c r="H319" s="7"/>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I319" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>319</v>
       </c>
@@ -8272,8 +9267,11 @@
       </c>
       <c r="G320" s="8"/>
       <c r="H320" s="8"/>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I320" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>320</v>
       </c>
@@ -8292,8 +9290,11 @@
       </c>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I321" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>321</v>
       </c>
@@ -8312,8 +9313,11 @@
       </c>
       <c r="G322" s="8"/>
       <c r="H322" s="8"/>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I322" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>322</v>
       </c>
@@ -8332,8 +9336,11 @@
       </c>
       <c r="G323" s="7"/>
       <c r="H323" s="7"/>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I323" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>323</v>
       </c>
@@ -8352,8 +9359,11 @@
       </c>
       <c r="G324" s="8"/>
       <c r="H324" s="8"/>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I324" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>324</v>
       </c>
@@ -8372,8 +9382,11 @@
       </c>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I325" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>325</v>
       </c>
@@ -8390,8 +9403,11 @@
       </c>
       <c r="G326" s="8"/>
       <c r="H326" s="8"/>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I326" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>326</v>
       </c>
@@ -8410,8 +9426,11 @@
       </c>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I327" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>327</v>
       </c>
@@ -8430,8 +9449,11 @@
       </c>
       <c r="G328" s="8"/>
       <c r="H328" s="8"/>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I328" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>328</v>
       </c>
@@ -8450,8 +9472,11 @@
       </c>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I329" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>329</v>
       </c>
@@ -8470,8 +9495,11 @@
       </c>
       <c r="G330" s="8"/>
       <c r="H330" s="8"/>
-    </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I330" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>330</v>
       </c>
@@ -8490,8 +9518,11 @@
       </c>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
-    </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I331" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>331</v>
       </c>
@@ -8510,8 +9541,11 @@
       </c>
       <c r="G332" s="8"/>
       <c r="H332" s="8"/>
-    </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I332" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>332</v>
       </c>
@@ -8530,8 +9564,11 @@
       </c>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
-    </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I333" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>333</v>
       </c>
@@ -8550,8 +9587,11 @@
       </c>
       <c r="G334" s="8"/>
       <c r="H334" s="8"/>
-    </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I334" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>334</v>
       </c>
@@ -8570,8 +9610,11 @@
       </c>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
-    </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I335" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>335</v>
       </c>
@@ -8590,8 +9633,11 @@
       </c>
       <c r="G336" s="8"/>
       <c r="H336" s="8"/>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I336" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>336</v>
       </c>
@@ -8610,8 +9656,11 @@
       </c>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I337" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>337</v>
       </c>
@@ -8630,8 +9679,11 @@
       </c>
       <c r="G338" s="8"/>
       <c r="H338" s="8"/>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I338" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>338</v>
       </c>
@@ -8650,8 +9702,11 @@
       </c>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I339" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>339</v>
       </c>
@@ -8670,8 +9725,11 @@
       </c>
       <c r="G340" s="8"/>
       <c r="H340" s="8"/>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I340" s="12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>340</v>
       </c>
@@ -8692,8 +9750,11 @@
       </c>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I341" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>341</v>
       </c>
@@ -8712,8 +9773,11 @@
       </c>
       <c r="G342" s="8"/>
       <c r="H342" s="8"/>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I342" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>342</v>
       </c>
@@ -8732,8 +9796,11 @@
       </c>
       <c r="G343" s="7"/>
       <c r="H343" s="7"/>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I343" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>343</v>
       </c>
@@ -8752,8 +9819,11 @@
       </c>
       <c r="G344" s="8"/>
       <c r="H344" s="8"/>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I344" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>344</v>
       </c>
@@ -8772,8 +9842,11 @@
       </c>
       <c r="G345" s="7"/>
       <c r="H345" s="7"/>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I345" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>345</v>
       </c>
@@ -8792,8 +9865,11 @@
       </c>
       <c r="G346" s="8"/>
       <c r="H346" s="8"/>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I346" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>346</v>
       </c>
@@ -8812,8 +9888,11 @@
       </c>
       <c r="G347" s="7"/>
       <c r="H347" s="7"/>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I347" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>347</v>
       </c>
@@ -8832,8 +9911,11 @@
       </c>
       <c r="G348" s="8"/>
       <c r="H348" s="8"/>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I348" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>348</v>
       </c>
@@ -8852,8 +9934,11 @@
       </c>
       <c r="G349" s="7"/>
       <c r="H349" s="7"/>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I349" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>349</v>
       </c>
@@ -8870,8 +9955,11 @@
       <c r="F350" s="8"/>
       <c r="G350" s="8"/>
       <c r="H350" s="8"/>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I350" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>350</v>
       </c>
@@ -8890,8 +9978,11 @@
       </c>
       <c r="G351" s="7"/>
       <c r="H351" s="7"/>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I351" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>351</v>
       </c>
@@ -8910,8 +10001,11 @@
       </c>
       <c r="G352" s="8"/>
       <c r="H352" s="8"/>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I352" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>352</v>
       </c>
@@ -8930,8 +10024,11 @@
       </c>
       <c r="G353" s="7"/>
       <c r="H353" s="7"/>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I353" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>353</v>
       </c>
@@ -8950,8 +10047,11 @@
       </c>
       <c r="G354" s="8"/>
       <c r="H354" s="8"/>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I354" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>354</v>
       </c>
@@ -8970,8 +10070,11 @@
       </c>
       <c r="G355" s="7"/>
       <c r="H355" s="7"/>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I355" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>355</v>
       </c>
@@ -8990,8 +10093,11 @@
       </c>
       <c r="G356" s="8"/>
       <c r="H356" s="8"/>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I356" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>356</v>
       </c>
@@ -9010,8 +10116,11 @@
       </c>
       <c r="G357" s="7"/>
       <c r="H357" s="7"/>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I357" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>357</v>
       </c>
@@ -9030,8 +10139,11 @@
       </c>
       <c r="G358" s="8"/>
       <c r="H358" s="8"/>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I358" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>358</v>
       </c>
@@ -9050,8 +10162,11 @@
       </c>
       <c r="G359" s="7"/>
       <c r="H359" s="7"/>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I359" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>359</v>
       </c>
@@ -9070,8 +10185,11 @@
       </c>
       <c r="G360" s="8"/>
       <c r="H360" s="8"/>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I360" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>360</v>
       </c>
@@ -9090,8 +10208,11 @@
       </c>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I361" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>361</v>
       </c>
@@ -9110,8 +10231,11 @@
       </c>
       <c r="G362" s="8"/>
       <c r="H362" s="8"/>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I362" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -9130,8 +10254,11 @@
       </c>
       <c r="G363" s="7"/>
       <c r="H363" s="7"/>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I363" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>363</v>
       </c>
@@ -9150,8 +10277,11 @@
       </c>
       <c r="G364" s="8"/>
       <c r="H364" s="8"/>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I364" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>364</v>
       </c>
@@ -9170,8 +10300,11 @@
       </c>
       <c r="G365" s="7"/>
       <c r="H365" s="7"/>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I365" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>365</v>
       </c>
@@ -9190,8 +10323,11 @@
       </c>
       <c r="G366" s="8"/>
       <c r="H366" s="8"/>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I366" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>366</v>
       </c>
@@ -9210,8 +10346,11 @@
       </c>
       <c r="G367" s="7"/>
       <c r="H367" s="7"/>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I367" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>367</v>
       </c>
@@ -9230,8 +10369,11 @@
       </c>
       <c r="G368" s="8"/>
       <c r="H368" s="8"/>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I368" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>368</v>
       </c>
@@ -9250,8 +10392,11 @@
       </c>
       <c r="G369" s="7"/>
       <c r="H369" s="7"/>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I369" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>369</v>
       </c>
@@ -9270,8 +10415,11 @@
       </c>
       <c r="G370" s="8"/>
       <c r="H370" s="8"/>
-    </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I370" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>370</v>
       </c>
@@ -9290,8 +10438,11 @@
       </c>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
-    </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I371" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>371</v>
       </c>
@@ -9310,8 +10461,11 @@
       </c>
       <c r="G372" s="8"/>
       <c r="H372" s="8"/>
-    </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I372" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>372</v>
       </c>
@@ -9330,8 +10484,11 @@
       </c>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
-    </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I373" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>373</v>
       </c>
@@ -9350,8 +10507,11 @@
       </c>
       <c r="G374" s="8"/>
       <c r="H374" s="8"/>
-    </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I374" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>374</v>
       </c>
@@ -9370,8 +10530,11 @@
       </c>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
-    </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I375" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>375</v>
       </c>
@@ -9390,8 +10553,11 @@
       </c>
       <c r="G376" s="8"/>
       <c r="H376" s="8"/>
-    </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I376" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>376</v>
       </c>
@@ -9410,8 +10576,11 @@
       </c>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
-    </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I377" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>377</v>
       </c>
@@ -9430,8 +10599,11 @@
       </c>
       <c r="G378" s="8"/>
       <c r="H378" s="8"/>
-    </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I378" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>378</v>
       </c>
@@ -9450,8 +10622,11 @@
       </c>
       <c r="G379" s="7"/>
       <c r="H379" s="7"/>
-    </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I379" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>379</v>
       </c>
@@ -9476,8 +10651,11 @@
       <c r="H380" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I380" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>380</v>
       </c>
@@ -9500,8 +10678,11 @@
       <c r="H381" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I381" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>381</v>
       </c>
@@ -9522,8 +10703,11 @@
       <c r="H382" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I382" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>382</v>
       </c>
@@ -9542,8 +10726,11 @@
       </c>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
-    </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I383" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>383</v>
       </c>
@@ -9564,8 +10751,11 @@
       </c>
       <c r="G384" s="8"/>
       <c r="H384" s="8"/>
-    </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I384" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>384</v>
       </c>
@@ -9586,8 +10776,11 @@
         <v>1</v>
       </c>
       <c r="H385" s="7"/>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I385" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>385</v>
       </c>
@@ -9608,8 +10801,11 @@
         <v>1</v>
       </c>
       <c r="H386" s="8"/>
-    </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I386" s="12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>386</v>
       </c>
@@ -9628,8 +10824,11 @@
       </c>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
-    </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I387" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>387</v>
       </c>
@@ -9648,8 +10847,11 @@
       </c>
       <c r="G388" s="8"/>
       <c r="H388" s="8"/>
-    </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I388" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>388</v>
       </c>
@@ -9670,8 +10872,11 @@
         <v>0</v>
       </c>
       <c r="H389" s="7"/>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I389" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>389</v>
       </c>
@@ -9692,8 +10897,11 @@
         <v>1</v>
       </c>
       <c r="H390" s="8"/>
-    </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I390" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>390</v>
       </c>
@@ -9714,8 +10922,11 @@
       </c>
       <c r="G391" s="7"/>
       <c r="H391" s="7"/>
-    </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I391" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>391</v>
       </c>
@@ -9736,8 +10947,11 @@
         <v>0</v>
       </c>
       <c r="H392" s="8"/>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I392" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>392</v>
       </c>
@@ -9756,8 +10970,11 @@
       </c>
       <c r="G393" s="7"/>
       <c r="H393" s="7"/>
-    </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I393" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>393</v>
       </c>
@@ -9780,8 +10997,11 @@
       <c r="H394" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I394" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>394</v>
       </c>
@@ -9800,8 +11020,11 @@
       </c>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
-    </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I395" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>395</v>
       </c>
@@ -9820,8 +11043,11 @@
       </c>
       <c r="G396" s="8"/>
       <c r="H396" s="8"/>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I396" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>396</v>
       </c>
@@ -9840,8 +11066,11 @@
       </c>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
-    </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I397" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>397</v>
       </c>
@@ -9860,8 +11089,11 @@
       </c>
       <c r="G398" s="8"/>
       <c r="H398" s="8"/>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I398" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>398</v>
       </c>
@@ -9882,8 +11114,11 @@
       </c>
       <c r="G399" s="7"/>
       <c r="H399" s="7"/>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I399" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>399</v>
       </c>
@@ -9902,8 +11137,11 @@
       </c>
       <c r="G400" s="8"/>
       <c r="H400" s="8"/>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I400" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>400</v>
       </c>
@@ -9922,8 +11160,11 @@
       </c>
       <c r="G401" s="7"/>
       <c r="H401" s="7"/>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I401" s="12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>401</v>
       </c>
@@ -9942,8 +11183,11 @@
       </c>
       <c r="G402" s="8"/>
       <c r="H402" s="8"/>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I402" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>402</v>
       </c>
@@ -9962,8 +11206,11 @@
       </c>
       <c r="G403" s="7"/>
       <c r="H403" s="7"/>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I403" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -9982,8 +11229,11 @@
       </c>
       <c r="G404" s="8"/>
       <c r="H404" s="8"/>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I404" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>404</v>
       </c>
@@ -10002,8 +11252,11 @@
       </c>
       <c r="G405" s="7"/>
       <c r="H405" s="7"/>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I405" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>405</v>
       </c>
@@ -10020,8 +11273,11 @@
       <c r="F406" s="8"/>
       <c r="G406" s="8"/>
       <c r="H406" s="8"/>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I406" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>406</v>
       </c>
@@ -10040,8 +11296,11 @@
       </c>
       <c r="G407" s="7"/>
       <c r="H407" s="7"/>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I407" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>407</v>
       </c>
@@ -10060,8 +11319,11 @@
       </c>
       <c r="G408" s="8"/>
       <c r="H408" s="8"/>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I408" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>408</v>
       </c>
@@ -10080,8 +11342,11 @@
       </c>
       <c r="G409" s="7"/>
       <c r="H409" s="7"/>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I409" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>409</v>
       </c>
@@ -10098,8 +11363,11 @@
       <c r="F410" s="8"/>
       <c r="G410" s="8"/>
       <c r="H410" s="8"/>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I410" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>410</v>
       </c>
@@ -10118,8 +11386,11 @@
       </c>
       <c r="G411" s="7"/>
       <c r="H411" s="7"/>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I411" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>411</v>
       </c>
@@ -10138,8 +11409,11 @@
       </c>
       <c r="G412" s="8"/>
       <c r="H412" s="8"/>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I412" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>412</v>
       </c>
@@ -10158,8 +11432,11 @@
       </c>
       <c r="G413" s="7"/>
       <c r="H413" s="7"/>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I413" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>413</v>
       </c>
@@ -10178,8 +11455,11 @@
       </c>
       <c r="G414" s="8"/>
       <c r="H414" s="8"/>
-    </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I414" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>414</v>
       </c>
@@ -10198,8 +11478,11 @@
       </c>
       <c r="G415" s="7"/>
       <c r="H415" s="7"/>
-    </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I415" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>415</v>
       </c>
@@ -10218,8 +11501,11 @@
       </c>
       <c r="G416" s="8"/>
       <c r="H416" s="8"/>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I416" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>416</v>
       </c>
@@ -10238,8 +11524,11 @@
       </c>
       <c r="G417" s="7"/>
       <c r="H417" s="7"/>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I417" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>417</v>
       </c>
@@ -10258,8 +11547,11 @@
       </c>
       <c r="G418" s="8"/>
       <c r="H418" s="8"/>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I418" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>418</v>
       </c>
@@ -10278,8 +11570,11 @@
       </c>
       <c r="G419" s="7"/>
       <c r="H419" s="7"/>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I419" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>419</v>
       </c>
@@ -10298,8 +11593,11 @@
       </c>
       <c r="G420" s="8"/>
       <c r="H420" s="8"/>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I420" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>420</v>
       </c>
@@ -10318,8 +11616,11 @@
       </c>
       <c r="G421" s="7"/>
       <c r="H421" s="7"/>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I421" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>421</v>
       </c>
@@ -10338,8 +11639,11 @@
       </c>
       <c r="G422" s="8"/>
       <c r="H422" s="8"/>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I422" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>422</v>
       </c>
@@ -10358,8 +11662,11 @@
       </c>
       <c r="G423" s="7"/>
       <c r="H423" s="7"/>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I423" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>423</v>
       </c>
@@ -10378,8 +11685,11 @@
       </c>
       <c r="G424" s="8"/>
       <c r="H424" s="8"/>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I424" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>424</v>
       </c>
@@ -10398,8 +11708,11 @@
       </c>
       <c r="G425" s="7"/>
       <c r="H425" s="7"/>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I425" s="12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>426</v>
       </c>
@@ -10420,8 +11733,11 @@
         <v>2</v>
       </c>
       <c r="H426" s="1"/>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I426" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>427</v>
       </c>
@@ -10442,8 +11758,11 @@
       </c>
       <c r="G427" s="8"/>
       <c r="H427" s="1"/>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I427" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>428</v>
       </c>
@@ -10464,8 +11783,11 @@
         <v>0</v>
       </c>
       <c r="H428" s="1"/>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I428" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>429</v>
       </c>
@@ -10486,8 +11808,11 @@
         <v>0</v>
       </c>
       <c r="H429" s="1"/>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I429" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>430</v>
       </c>
@@ -10508,8 +11833,11 @@
         <v>0</v>
       </c>
       <c r="H430" s="1"/>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I430" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>431</v>
       </c>
@@ -10530,8 +11858,11 @@
         <v>0</v>
       </c>
       <c r="H431" s="1"/>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I431" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>432</v>
       </c>
@@ -10552,8 +11883,11 @@
         <v>1</v>
       </c>
       <c r="H432" s="1"/>
-    </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I432" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>433</v>
       </c>
@@ -10574,8 +11908,11 @@
         <v>1</v>
       </c>
       <c r="H433" s="1"/>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I433" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>434</v>
       </c>
@@ -10598,8 +11935,11 @@
         <v>1</v>
       </c>
       <c r="H434" s="1"/>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I434" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>435</v>
       </c>
@@ -10622,8 +11962,11 @@
         <v>1</v>
       </c>
       <c r="H435" s="1"/>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I435" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>436</v>
       </c>
@@ -10644,8 +11987,11 @@
         <v>2</v>
       </c>
       <c r="H436" s="1"/>
-    </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I436" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>437</v>
       </c>
@@ -10666,8 +12012,11 @@
         <v>0</v>
       </c>
       <c r="H437" s="8"/>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I437" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>438</v>
       </c>
@@ -10688,8 +12037,11 @@
         <v>0</v>
       </c>
       <c r="H438" s="7"/>
-    </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I438" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>439</v>
       </c>
@@ -10710,8 +12062,11 @@
         <v>0</v>
       </c>
       <c r="H439" s="8"/>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I439" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>440</v>
       </c>
@@ -10732,8 +12087,11 @@
         <v>1</v>
       </c>
       <c r="H440" s="7"/>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I440" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>441</v>
       </c>
@@ -10754,8 +12112,11 @@
         <v>0</v>
       </c>
       <c r="H441" s="8"/>
-    </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I441" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>442</v>
       </c>
@@ -10776,8 +12137,11 @@
         <v>0</v>
       </c>
       <c r="H442" s="7"/>
-    </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I442" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>443</v>
       </c>
@@ -10798,8 +12162,11 @@
         <v>1</v>
       </c>
       <c r="H443" s="7"/>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I443" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>444</v>
       </c>
@@ -10820,8 +12187,11 @@
         <v>1</v>
       </c>
       <c r="H444" s="8"/>
-    </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I444" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A445" s="1"/>
       <c r="B445" s="8"/>
       <c r="C445" s="6">
@@ -10840,8 +12210,11 @@
         <v>1</v>
       </c>
       <c r="H445" s="8"/>
-    </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I445" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>425</v>
       </c>
@@ -10860,8 +12233,11 @@
       </c>
       <c r="G446" s="8"/>
       <c r="H446" s="8"/>
-    </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I446" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>446</v>
       </c>
@@ -10880,8 +12256,11 @@
       </c>
       <c r="G447" s="7"/>
       <c r="H447" s="8"/>
-    </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I447" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>447</v>
       </c>
@@ -10900,8 +12279,11 @@
       </c>
       <c r="G448" s="8"/>
       <c r="H448" s="7"/>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I448" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>448</v>
       </c>
@@ -10920,8 +12302,11 @@
       </c>
       <c r="G449" s="7"/>
       <c r="H449" s="8"/>
-    </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I449" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>449</v>
       </c>
@@ -10942,8 +12327,11 @@
         <v>1</v>
       </c>
       <c r="H450" s="7"/>
-    </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I450" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>450</v>
       </c>
@@ -10962,8 +12350,11 @@
       </c>
       <c r="G451" s="7"/>
       <c r="H451" s="8"/>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I451" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>451</v>
       </c>
@@ -10982,8 +12373,11 @@
       </c>
       <c r="G452" s="8"/>
       <c r="H452" s="7"/>
-    </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I452" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>452</v>
       </c>
@@ -11002,8 +12396,11 @@
       </c>
       <c r="G453" s="7"/>
       <c r="H453" s="8"/>
-    </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I453" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>453</v>
       </c>
@@ -11022,8 +12419,11 @@
       </c>
       <c r="G454" s="8"/>
       <c r="H454" s="7"/>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I454" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>454</v>
       </c>
@@ -11042,8 +12442,11 @@
       </c>
       <c r="G455" s="7"/>
       <c r="H455" s="8"/>
-    </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I455" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>455</v>
       </c>
@@ -11062,8 +12465,11 @@
       </c>
       <c r="G456" s="8"/>
       <c r="H456" s="7"/>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I456" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>456</v>
       </c>
@@ -11082,8 +12488,11 @@
       </c>
       <c r="G457" s="7"/>
       <c r="H457" s="8"/>
-    </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I457" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>457</v>
       </c>
@@ -11102,8 +12511,11 @@
       </c>
       <c r="G458" s="8"/>
       <c r="H458" s="7"/>
-    </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I458" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>458</v>
       </c>
@@ -11122,8 +12534,11 @@
       </c>
       <c r="G459" s="7"/>
       <c r="H459" s="8"/>
-    </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I459" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>459</v>
       </c>
@@ -11142,8 +12557,11 @@
       </c>
       <c r="G460" s="8"/>
       <c r="H460" s="7"/>
-    </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I460" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>460</v>
       </c>
@@ -11162,8 +12580,11 @@
       </c>
       <c r="G461" s="7"/>
       <c r="H461" s="8"/>
-    </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I461" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>461</v>
       </c>
@@ -11182,8 +12603,11 @@
       </c>
       <c r="G462" s="8"/>
       <c r="H462" s="7"/>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I462" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>462</v>
       </c>
@@ -11202,8 +12626,11 @@
       </c>
       <c r="G463" s="7"/>
       <c r="H463" s="8"/>
-    </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I463" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>463</v>
       </c>
@@ -11222,8 +12649,11 @@
       </c>
       <c r="G464" s="8"/>
       <c r="H464" s="7"/>
-    </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I464" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>464</v>
       </c>
@@ -11242,8 +12672,11 @@
       </c>
       <c r="G465" s="7"/>
       <c r="H465" s="8"/>
-    </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I465" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>465</v>
       </c>
@@ -11262,8 +12695,11 @@
       </c>
       <c r="G466" s="8"/>
       <c r="H466" s="7"/>
-    </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I466" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>466</v>
       </c>
@@ -11282,8 +12718,11 @@
       </c>
       <c r="G467" s="7"/>
       <c r="H467" s="8"/>
-    </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I467" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>467</v>
       </c>
@@ -11302,8 +12741,11 @@
       </c>
       <c r="G468" s="8"/>
       <c r="H468" s="7"/>
-    </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I468" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>468</v>
       </c>
@@ -11322,8 +12764,11 @@
       </c>
       <c r="G469" s="7"/>
       <c r="H469" s="8"/>
-    </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I469" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>469</v>
       </c>
@@ -11342,8 +12787,11 @@
       </c>
       <c r="G470" s="8"/>
       <c r="H470" s="7"/>
-    </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I470" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>470</v>
       </c>
@@ -11362,8 +12810,11 @@
       </c>
       <c r="G471" s="7"/>
       <c r="H471" s="8"/>
-    </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I471" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>471</v>
       </c>
@@ -11382,8 +12833,11 @@
       </c>
       <c r="G472" s="8"/>
       <c r="H472" s="7"/>
-    </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I472" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>472</v>
       </c>
@@ -11402,8 +12856,11 @@
       </c>
       <c r="G473" s="7"/>
       <c r="H473" s="8"/>
-    </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I473" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>473</v>
       </c>
@@ -11422,8 +12879,11 @@
       </c>
       <c r="G474" s="8"/>
       <c r="H474" s="7"/>
-    </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I474" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>474</v>
       </c>
@@ -11442,8 +12902,11 @@
       </c>
       <c r="G475" s="7"/>
       <c r="H475" s="8"/>
-    </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I475" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>475</v>
       </c>
@@ -11462,8 +12925,11 @@
       </c>
       <c r="G476" s="8"/>
       <c r="H476" s="7"/>
-    </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I476" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>476</v>
       </c>
@@ -11482,8 +12948,11 @@
       </c>
       <c r="G477" s="7"/>
       <c r="H477" s="8"/>
-    </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I477" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>477</v>
       </c>
@@ -11502,8 +12971,11 @@
       </c>
       <c r="G478" s="8"/>
       <c r="H478" s="7"/>
-    </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I478" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>478</v>
       </c>
@@ -11522,8 +12994,11 @@
       </c>
       <c r="G479" s="7"/>
       <c r="H479" s="8"/>
-    </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I479" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>479</v>
       </c>
@@ -11542,8 +13017,11 @@
       </c>
       <c r="G480" s="8"/>
       <c r="H480" s="7"/>
-    </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I480" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>480</v>
       </c>
@@ -11562,8 +13040,11 @@
       </c>
       <c r="G481" s="7"/>
       <c r="H481" s="8"/>
-    </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I481" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>481</v>
       </c>
@@ -11580,8 +13061,11 @@
       </c>
       <c r="G482" s="8"/>
       <c r="H482" s="7"/>
-    </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I482" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>482</v>
       </c>
@@ -11600,8 +13084,11 @@
       </c>
       <c r="G483" s="7"/>
       <c r="H483" s="8"/>
-    </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I483" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>483</v>
       </c>
@@ -11618,8 +13105,11 @@
       <c r="F484" s="8"/>
       <c r="G484" s="8"/>
       <c r="H484" s="7"/>
-    </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I484" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>484</v>
       </c>
@@ -11638,8 +13128,11 @@
       </c>
       <c r="G485" s="7"/>
       <c r="H485" s="8"/>
-    </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I485" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>485</v>
       </c>
@@ -11658,8 +13151,11 @@
       </c>
       <c r="G486" s="8"/>
       <c r="H486" s="7"/>
-    </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I486" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>486</v>
       </c>
@@ -11678,8 +13174,11 @@
       </c>
       <c r="G487" s="7"/>
       <c r="H487" s="8"/>
-    </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I487" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>487</v>
       </c>
@@ -11698,8 +13197,11 @@
       </c>
       <c r="G488" s="8"/>
       <c r="H488" s="7"/>
-    </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I488" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>488</v>
       </c>
@@ -11718,8 +13220,11 @@
       </c>
       <c r="G489" s="7"/>
       <c r="H489" s="8"/>
-    </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I489" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>489</v>
       </c>
@@ -11738,8 +13243,11 @@
       </c>
       <c r="G490" s="8"/>
       <c r="H490" s="7"/>
-    </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I490" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="491" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>490</v>
       </c>
@@ -11758,8 +13266,11 @@
       </c>
       <c r="G491" s="7"/>
       <c r="H491" s="8"/>
-    </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I491" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="492" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>491</v>
       </c>
@@ -11778,8 +13289,11 @@
       </c>
       <c r="G492" s="8"/>
       <c r="H492" s="7"/>
-    </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I492" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>492</v>
       </c>
@@ -11798,8 +13312,11 @@
       </c>
       <c r="G493" s="7"/>
       <c r="H493" s="8"/>
-    </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I493" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>493</v>
       </c>
@@ -11818,8 +13335,11 @@
       </c>
       <c r="G494" s="8"/>
       <c r="H494" s="7"/>
-    </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I494" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>494</v>
       </c>
@@ -11838,8 +13358,11 @@
       </c>
       <c r="G495" s="7"/>
       <c r="H495" s="1"/>
-    </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I495" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>495</v>
       </c>
@@ -11858,8 +13381,11 @@
       </c>
       <c r="G496" s="8"/>
       <c r="H496" s="1"/>
-    </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I496" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="497" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>496</v>
       </c>
@@ -11878,8 +13404,11 @@
       </c>
       <c r="G497" s="7"/>
       <c r="H497" s="1"/>
-    </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I497" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="498" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>497</v>
       </c>
@@ -11898,8 +13427,11 @@
       </c>
       <c r="G498" s="8"/>
       <c r="H498" s="1"/>
-    </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I498" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>498</v>
       </c>
@@ -11918,8 +13450,11 @@
       </c>
       <c r="G499" s="7"/>
       <c r="H499" s="1"/>
-    </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I499" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>499</v>
       </c>
@@ -11938,8 +13473,11 @@
       </c>
       <c r="G500" s="8"/>
       <c r="H500" s="1"/>
-    </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I500" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="501" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>500</v>
       </c>
@@ -11958,8 +13496,11 @@
       </c>
       <c r="G501" s="7"/>
       <c r="H501" s="1"/>
-    </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I501" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="502" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>501</v>
       </c>
@@ -11978,8 +13519,11 @@
       </c>
       <c r="G502" s="8"/>
       <c r="H502" s="1"/>
-    </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I502" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>502</v>
       </c>
@@ -11998,8 +13542,11 @@
       </c>
       <c r="G503" s="7"/>
       <c r="H503" s="1"/>
-    </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I503" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>503</v>
       </c>
@@ -12018,8 +13565,11 @@
       </c>
       <c r="G504" s="8"/>
       <c r="H504" s="1"/>
-    </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I504" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>504</v>
       </c>
@@ -12038,8 +13588,11 @@
       </c>
       <c r="G505" s="7"/>
       <c r="H505" s="1"/>
-    </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I505" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>505</v>
       </c>
@@ -12058,8 +13611,11 @@
       </c>
       <c r="G506" s="8"/>
       <c r="H506" s="1"/>
-    </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I506" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="507" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>506</v>
       </c>
@@ -12078,8 +13634,11 @@
       </c>
       <c r="G507" s="7"/>
       <c r="H507" s="1"/>
-    </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I507" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>507</v>
       </c>
@@ -12098,8 +13657,11 @@
       </c>
       <c r="G508" s="8"/>
       <c r="H508" s="1"/>
-    </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I508" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>508</v>
       </c>
@@ -12118,8 +13680,11 @@
       </c>
       <c r="G509" s="7"/>
       <c r="H509" s="1"/>
-    </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I509" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>509</v>
       </c>
@@ -12138,8 +13703,11 @@
       </c>
       <c r="G510" s="8"/>
       <c r="H510" s="1"/>
-    </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I510" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="511" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>510</v>
       </c>
@@ -12158,8 +13726,11 @@
       </c>
       <c r="G511" s="7"/>
       <c r="H511" s="1"/>
-    </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I511" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="512" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>511</v>
       </c>
@@ -12178,8 +13749,11 @@
       </c>
       <c r="G512" s="8"/>
       <c r="H512" s="1"/>
-    </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I512" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>512</v>
       </c>
@@ -12198,6 +13772,12 @@
       </c>
       <c r="G513" s="7"/>
       <c r="H513" s="1"/>
+      <c r="I513" s="12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I514" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
